--- a/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_05-15-2025.xlsx
+++ b/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_05-15-2025.xlsx
@@ -8,19 +8,584 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Core-Products_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42E6906-54A5-40BE-9587-3586223B9E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123677A8-95F1-4144-AA0E-32FDA391F584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{4E09D107-23F0-48DD-9847-35EDEB095A52}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-34.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{852D977E-91BB-4466-BFB6-335E9E2BD4DF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-34.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{D96BCEB7-7AA0-4105-8735-0A5AC7B00A23}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-34.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0" shapeId="0" xr:uid="{32FDE2AE-63F1-4759-92D4-FAA632BADD27}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-34.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N4" authorId="0" shapeId="0" xr:uid="{599379A8-6BCF-4DEB-BDCE-C46F7368E5BB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-34.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{4F30907E-45B5-42CD-BDD1-C057653C15C2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-34.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N5" authorId="0" shapeId="0" xr:uid="{8C57ED0C-20D1-4CA7-BC95-C8FEB8698681}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-34.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N7" authorId="0" shapeId="0" xr:uid="{C8BA7E7B-32C1-45BE-83BB-B3A3A5C9391C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-48.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N8" authorId="0" shapeId="0" xr:uid="{36E9308D-E70A-4E53-A0C3-F3DEBCD9AB37}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-75.24 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{8324CD29-805E-4B30-87E1-15DE65307F59}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-59.99 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{25255956-A722-4D9D-AA59-C6E01292DA25}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-41.66 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N10" authorId="0" shapeId="0" xr:uid="{561FB985-51D4-49BC-8643-6C1A9F5C20F6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-36.42 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{0600FE98-AD5A-478E-A89C-A80320DD17A8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-39.73 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{34A567F5-5A26-482F-8D5C-6341CDC13890}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-41.66 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N15" authorId="0" shapeId="0" xr:uid="{B9C4C0D3-9537-4B60-9FF5-3B5442A1AF50}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-33.00 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N16" authorId="0" shapeId="0" xr:uid="{E4244E1D-4630-49D5-AE41-3CF3792D44B6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-35.67 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N17" authorId="0" shapeId="0" xr:uid="{3162A2B2-A2CA-4408-8ABC-C0AF2D314A23}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-38.00 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{F5DC98F5-7407-4440-B5D5-E4D8E7D27203}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-28.50 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N19" authorId="0" shapeId="0" xr:uid="{FFED1F26-895D-4ADE-8209-140F599714F1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-48.70 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{ED317284-520D-4433-9AC5-2F4AF39BEB2F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-47.39 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N22" authorId="0" shapeId="0" xr:uid="{6DCF5DD8-FB1C-4A9F-AFA5-2BF1F3104FBD}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-33.30 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N23" authorId="0" shapeId="0" xr:uid="{63AC180F-4769-47D6-A5C3-01E28C60668F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-780.24 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N24" authorId="0" shapeId="0" xr:uid="{04C0492A-E7AC-4D6C-8A32-CA6BC0EA7867}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-748.99 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N25" authorId="0" shapeId="0" xr:uid="{D4E8249D-138E-476E-BDB5-1A4676EF1DF8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-560.18 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N26" authorId="0" shapeId="0" xr:uid="{0394787E-DBB2-48B3-B293-4F5F92D8525F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-563.16 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{79A32576-D31C-4926-BE67-ED96EBA80B2F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-519.9 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N27" authorId="0" shapeId="0" xr:uid="{3BC06C8B-B638-4F4C-9785-BC3C79B60AB0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-499.56 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N28" authorId="0" shapeId="0" xr:uid="{DEDC1BBF-652D-4080-9658-93506B8984C5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-798.00 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N29" authorId="0" shapeId="0" xr:uid="{076DFDEF-6805-48C1-9233-CF909DAF6E06}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-168.00 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N30" authorId="0" shapeId="0" xr:uid="{C7A2248C-909A-464C-90E4-8BCF6386FEBE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-179.22 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N31" authorId="0" shapeId="0" xr:uid="{420862B0-CC47-4F56-8AF3-872FE58115D2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-155.29 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N32" authorId="0" shapeId="0" xr:uid="{9376FB0B-6C91-4339-AA0B-00CD45E08582}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-144.89 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{057ADDEF-29F3-4092-87AF-11B4F4AD4A1F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-184.20 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N34" authorId="0" shapeId="0" xr:uid="{FCE5CDA0-A774-4E18-83BC-F4B60367E486}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-140.60 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{0415DCB2-58EC-4F8F-A069-0CDDDAF2E9D6}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-84.95 ex vat
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N35" authorId="0" shapeId="0" xr:uid="{920F5407-056B-4A98-99EF-C8A39BBE3298}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-91.20 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N36" authorId="0" shapeId="0" xr:uid="{0E634F3A-F008-410F-B423-CF78139F79D5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Presale:-10.70 EX VAT
+======</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="314">
   <si>
     <t>SKU</t>
   </si>
@@ -983,12 +1548,15 @@
   <si>
     <t>£15.40</t>
   </si>
+  <si>
+    <t>N/A</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,13 +1569,65 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC0000"/>
+        <bgColor rgb="FFCC0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE06666"/>
+        <bgColor rgb="FFE06666"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1037,16 +1657,159 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00FF00"/>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1343,15 +2106,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="64.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1364,26 +2130,30 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1"/>
+      <c r="O1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1399,26 +2169,47 @@
       <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5">
+        <v>29.95</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" s="9">
+        <v>29.99</v>
+      </c>
+      <c r="I2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" s="5">
+        <v>27.88</v>
+      </c>
+      <c r="K2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" s="5">
+        <v>52.6</v>
+      </c>
+      <c r="M2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="N2" s="9">
+        <v>28.75</v>
+      </c>
+      <c r="O2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" s="5">
+        <v>28.96</v>
+      </c>
+      <c r="Q2" t="s">
         <v>19</v>
       </c>
+      <c r="R2" s="12">
+        <v>31.08</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1434,26 +2225,47 @@
       <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="5">
+        <v>29.95</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="9">
+        <v>29.99</v>
+      </c>
+      <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" s="5">
+        <v>28.53</v>
+      </c>
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" s="5">
+        <v>50.94</v>
+      </c>
+      <c r="M3" t="s">
         <v>17</v>
       </c>
-      <c r="J3" t="s">
+      <c r="N3" s="9">
+        <v>28.75</v>
+      </c>
+      <c r="O3" t="s">
         <v>18</v>
       </c>
-      <c r="K3" t="s">
+      <c r="P3" s="5">
+        <v>28.96</v>
+      </c>
+      <c r="Q3" t="s">
         <v>24</v>
       </c>
+      <c r="R3" s="12">
+        <v>31.58</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1469,26 +2281,47 @@
       <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="5">
+        <v>28.95</v>
+      </c>
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" s="5">
+        <v>43.33</v>
+      </c>
+      <c r="I4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" s="5">
+        <v>29.43</v>
+      </c>
+      <c r="K4" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="M4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" t="s">
+      <c r="N4" s="9">
+        <v>28.75</v>
+      </c>
+      <c r="O4" t="s">
         <v>31</v>
       </c>
-      <c r="K4" t="s">
-        <v>30</v>
+      <c r="P4" s="5">
+        <v>29.5</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>30</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>313</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1504,26 +2337,47 @@
       <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="5">
+        <v>29.95</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" s="9">
+        <v>29.99</v>
+      </c>
+      <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" s="5">
+        <v>28.46</v>
+      </c>
+      <c r="K5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" s="5">
+        <v>51.38</v>
+      </c>
+      <c r="M5" t="s">
         <v>17</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" s="9">
+        <v>28.75</v>
+      </c>
+      <c r="O5" t="s">
         <v>18</v>
       </c>
-      <c r="K5" t="s">
+      <c r="P5" s="5">
+        <v>28.96</v>
+      </c>
+      <c r="Q5" t="s">
         <v>36</v>
       </c>
+      <c r="R5" s="12">
+        <v>32.619999999999997</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1539,26 +2393,47 @@
       <c r="E6" t="s">
         <v>39</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="5">
+        <v>44.95</v>
+      </c>
+      <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" s="5">
+        <v>43.99</v>
+      </c>
+      <c r="I6" t="s">
         <v>41</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" s="5">
+        <v>43.7</v>
+      </c>
+      <c r="K6" t="s">
         <v>42</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" s="5">
+        <v>47.09</v>
+      </c>
+      <c r="M6" t="s">
         <v>43</v>
       </c>
-      <c r="J6" t="s">
+      <c r="N6" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O6" t="s">
         <v>44</v>
       </c>
-      <c r="K6" t="s">
+      <c r="P6" s="5">
+        <v>45.29</v>
+      </c>
+      <c r="Q6" t="s">
         <v>45</v>
       </c>
+      <c r="R6" s="12">
+        <v>43</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1574,26 +2449,47 @@
       <c r="E7" t="s">
         <v>48</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="5">
+        <v>43.5</v>
+      </c>
+      <c r="G7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" s="5">
+        <v>43.99</v>
+      </c>
+      <c r="I7" t="s">
         <v>49</v>
       </c>
-      <c r="H7" t="s">
+      <c r="J7" s="5">
+        <v>41.41</v>
+      </c>
+      <c r="K7" t="s">
         <v>50</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" s="5">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="M7" t="s">
         <v>51</v>
       </c>
-      <c r="J7" t="s">
+      <c r="N7" s="9">
+        <v>42.99</v>
+      </c>
+      <c r="O7" t="s">
         <v>52</v>
       </c>
-      <c r="K7" t="s">
+      <c r="P7" s="5">
+        <v>46.66</v>
+      </c>
+      <c r="Q7" t="s">
         <v>53</v>
       </c>
+      <c r="R7" s="12">
+        <v>44.99</v>
+      </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1609,26 +2505,47 @@
       <c r="E8" t="s">
         <v>56</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="5">
+        <v>56.95</v>
+      </c>
+      <c r="G8" t="s">
         <v>57</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" s="5">
+        <v>62.49</v>
+      </c>
+      <c r="I8" t="s">
         <v>58</v>
       </c>
-      <c r="H8" t="s">
+      <c r="J8" s="5">
+        <v>62.29</v>
+      </c>
+      <c r="K8" t="s">
         <v>59</v>
       </c>
-      <c r="I8" t="s">
+      <c r="L8" s="5">
+        <v>87.49</v>
+      </c>
+      <c r="M8" t="s">
         <v>60</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" s="9">
+        <v>59.99</v>
+      </c>
+      <c r="O8" t="s">
         <v>61</v>
       </c>
-      <c r="K8" t="s">
+      <c r="P8" s="5">
+        <v>60.03</v>
+      </c>
+      <c r="Q8" t="s">
         <v>62</v>
       </c>
+      <c r="R8" s="12">
+        <v>54.99</v>
+      </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1644,26 +2561,47 @@
       <c r="E9" t="s">
         <v>65</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="5">
+        <v>48.95</v>
+      </c>
+      <c r="G9" t="s">
         <v>66</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" s="5">
+        <v>59.99</v>
+      </c>
+      <c r="I9" t="s">
         <v>67</v>
       </c>
-      <c r="H9" t="s">
+      <c r="J9" s="5">
+        <v>57.78</v>
+      </c>
+      <c r="K9" t="s">
         <v>68</v>
       </c>
-      <c r="I9" t="s">
+      <c r="L9" s="5">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="M9" t="s">
         <v>69</v>
       </c>
-      <c r="J9" t="s">
+      <c r="N9" s="9">
+        <v>54.99</v>
+      </c>
+      <c r="O9" t="s">
         <v>70</v>
       </c>
-      <c r="K9" t="s">
+      <c r="P9" s="5">
+        <v>53.77</v>
+      </c>
+      <c r="Q9" t="s">
         <v>71</v>
       </c>
+      <c r="R9" s="12">
+        <v>53.99</v>
+      </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1679,26 +2617,47 @@
       <c r="E10" t="s">
         <v>74</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="5">
+        <v>34.950000000000003</v>
+      </c>
+      <c r="G10" t="s">
         <v>75</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" s="9">
+        <v>39.159999999999997</v>
+      </c>
+      <c r="I10" t="s">
         <v>76</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" s="5">
+        <v>33.332999999999998</v>
+      </c>
+      <c r="K10" t="s">
         <v>77</v>
       </c>
-      <c r="I10" t="s">
+      <c r="L10" s="5">
+        <v>48.05</v>
+      </c>
+      <c r="M10" t="s">
         <v>78</v>
       </c>
-      <c r="J10" t="s">
+      <c r="N10" s="9">
+        <v>34.17</v>
+      </c>
+      <c r="O10" t="s">
         <v>79</v>
       </c>
-      <c r="K10" t="s">
+      <c r="P10" s="5">
+        <v>35.43</v>
+      </c>
+      <c r="Q10" t="s">
         <v>80</v>
       </c>
+      <c r="R10" s="12">
+        <v>35.880000000000003</v>
+      </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1714,26 +2673,47 @@
       <c r="E11" t="s">
         <v>83</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="5">
+        <v>35.5</v>
+      </c>
+      <c r="G11" t="s">
         <v>84</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" s="5">
+        <v>63.91</v>
+      </c>
+      <c r="I11" t="s">
         <v>85</v>
       </c>
-      <c r="H11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" s="5">
+        <v>32</v>
+      </c>
+      <c r="K11" t="s">
+        <v>30</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M11" t="s">
         <v>86</v>
       </c>
-      <c r="J11" t="s">
+      <c r="N11" s="9">
+        <v>33.909999999999997</v>
+      </c>
+      <c r="O11" t="s">
         <v>87</v>
       </c>
-      <c r="K11" t="s">
+      <c r="P11" s="5">
+        <v>36.06</v>
+      </c>
+      <c r="Q11" t="s">
         <v>88</v>
       </c>
+      <c r="R11" s="12">
+        <v>36.880000000000003</v>
+      </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1749,26 +2729,47 @@
       <c r="E12" t="s">
         <v>91</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="5">
+        <v>17.5</v>
+      </c>
+      <c r="G12" t="s">
         <v>92</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" s="5">
+        <v>22.49</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="H12" t="s">
+      <c r="J12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" t="s">
         <v>93</v>
       </c>
-      <c r="I12" t="s">
+      <c r="L12" s="5">
+        <v>27.94</v>
+      </c>
+      <c r="M12" t="s">
         <v>94</v>
       </c>
-      <c r="J12" t="s">
+      <c r="N12" s="5">
+        <v>17.329999999999998</v>
+      </c>
+      <c r="O12" t="s">
         <v>95</v>
       </c>
-      <c r="K12" t="s">
-        <v>30</v>
+      <c r="P12" s="5">
+        <v>18.18</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R12" s="12" t="s">
+        <v>313</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1784,26 +2785,47 @@
       <c r="E13" t="s">
         <v>98</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="5">
+        <v>33.950000000000003</v>
+      </c>
+      <c r="G13" t="s">
         <v>99</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" s="9">
+        <v>33.33</v>
+      </c>
+      <c r="I13" t="s">
         <v>100</v>
       </c>
-      <c r="H13" t="s">
+      <c r="J13" s="5">
+        <v>32.08</v>
+      </c>
+      <c r="K13" t="s">
         <v>101</v>
       </c>
-      <c r="I13" t="s">
+      <c r="L13" s="5">
+        <v>60.31</v>
+      </c>
+      <c r="M13" t="s">
         <v>102</v>
       </c>
-      <c r="J13" t="s">
+      <c r="N13" s="5">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="O13" t="s">
         <v>103</v>
       </c>
-      <c r="K13" t="s">
+      <c r="P13" s="5">
+        <v>34.26</v>
+      </c>
+      <c r="Q13" t="s">
         <v>76</v>
       </c>
+      <c r="R13" s="13">
+        <v>33.33</v>
+      </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1819,26 +2841,53 @@
       <c r="E14" t="s">
         <v>30</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G14" t="s">
         <v>106</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" s="5">
+        <f>51.63*25</f>
+        <v>1290.75</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" s="5">
+        <f>34*25</f>
+        <v>850</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I14" t="s">
+      <c r="L14" s="5">
+        <f>49.71*25</f>
+        <v>1242.75</v>
+      </c>
+      <c r="M14" t="s">
         <v>109</v>
       </c>
-      <c r="J14" t="s">
+      <c r="N14" s="5">
+        <f>33.88*25</f>
+        <v>847.00000000000011</v>
+      </c>
+      <c r="O14" t="s">
         <v>110</v>
       </c>
-      <c r="K14" t="s">
+      <c r="P14" s="5">
+        <f>47.9*25</f>
+        <v>1197.5</v>
+      </c>
+      <c r="Q14" s="8" t="s">
         <v>109</v>
       </c>
+      <c r="R14" s="13">
+        <f>33.88*25</f>
+        <v>847.00000000000011</v>
+      </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1854,26 +2903,47 @@
       <c r="E15" t="s">
         <v>113</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="5">
+        <v>24.95</v>
+      </c>
+      <c r="G15" t="s">
         <v>114</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" s="5">
+        <v>28.59</v>
+      </c>
+      <c r="I15" t="s">
         <v>115</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" s="5">
+        <v>24.58</v>
+      </c>
+      <c r="K15" t="s">
         <v>116</v>
       </c>
-      <c r="I15" t="s">
+      <c r="L15" s="5">
+        <v>26.13</v>
+      </c>
+      <c r="M15" t="s">
         <v>117</v>
       </c>
-      <c r="J15" t="s">
+      <c r="N15" s="9">
+        <v>25.87</v>
+      </c>
+      <c r="O15" t="s">
         <v>118</v>
       </c>
-      <c r="K15" t="s">
+      <c r="P15" s="5">
+        <v>29.72</v>
+      </c>
+      <c r="Q15" t="s">
         <v>119</v>
       </c>
+      <c r="R15" s="12" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1889,26 +2959,47 @@
       <c r="E16" t="s">
         <v>122</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="5">
+        <v>27.5</v>
+      </c>
+      <c r="G16" t="s">
         <v>123</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" s="5">
+        <v>27.29</v>
+      </c>
+      <c r="I16" t="s">
         <v>124</v>
       </c>
-      <c r="H16" t="s">
+      <c r="J16" s="5">
+        <v>24.88</v>
+      </c>
+      <c r="K16" t="s">
         <v>125</v>
       </c>
-      <c r="I16" t="s">
+      <c r="L16" s="5">
+        <v>28.7</v>
+      </c>
+      <c r="M16" t="s">
         <v>126</v>
       </c>
-      <c r="J16" t="s">
+      <c r="N16" s="9">
+        <v>27.34</v>
+      </c>
+      <c r="O16" t="s">
         <v>127</v>
       </c>
-      <c r="K16" t="s">
+      <c r="P16" s="5">
+        <v>27.09</v>
+      </c>
+      <c r="Q16" t="s">
         <v>128</v>
       </c>
+      <c r="R16" s="12">
+        <v>27.24</v>
+      </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1924,26 +3015,47 @@
       <c r="E17" t="s">
         <v>122</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="5">
+        <v>27.5</v>
+      </c>
+      <c r="G17" t="s">
         <v>123</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" s="5">
+        <v>27.29</v>
+      </c>
+      <c r="I17" t="s">
         <v>131</v>
       </c>
-      <c r="H17" t="s">
+      <c r="J17" s="5">
+        <v>25.83</v>
+      </c>
+      <c r="K17" t="s">
         <v>132</v>
       </c>
-      <c r="I17" t="s">
+      <c r="L17" s="5">
+        <v>28.62</v>
+      </c>
+      <c r="M17" t="s">
         <v>133</v>
       </c>
-      <c r="J17" t="s">
+      <c r="N17" s="9">
+        <v>26.26</v>
+      </c>
+      <c r="O17" t="s">
         <v>134</v>
       </c>
-      <c r="K17" t="s">
+      <c r="P17" s="5">
+        <v>26.78</v>
+      </c>
+      <c r="Q17" t="s">
         <v>135</v>
       </c>
+      <c r="R17" s="12">
+        <v>25.74</v>
+      </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1959,26 +3071,47 @@
       <c r="E18" t="s">
         <v>138</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="5">
+        <v>21.5</v>
+      </c>
+      <c r="G18" t="s">
         <v>139</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" s="5">
+        <v>21.66</v>
+      </c>
+      <c r="I18" t="s">
         <v>140</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" s="5">
+        <v>21.46</v>
+      </c>
+      <c r="K18" t="s">
         <v>141</v>
       </c>
-      <c r="I18" t="s">
+      <c r="L18" s="5">
+        <v>24.72</v>
+      </c>
+      <c r="M18" t="s">
         <v>142</v>
       </c>
-      <c r="J18" t="s">
+      <c r="N18" s="9">
+        <v>22.8</v>
+      </c>
+      <c r="O18" t="s">
         <v>143</v>
       </c>
-      <c r="K18" t="s">
+      <c r="P18" s="5">
+        <v>23.33</v>
+      </c>
+      <c r="Q18" t="s">
         <v>144</v>
       </c>
+      <c r="R18" s="12">
+        <v>23.43</v>
+      </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1994,26 +3127,47 @@
       <c r="E19" t="s">
         <v>147</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="5">
+        <v>41.5</v>
+      </c>
+      <c r="G19" t="s">
         <v>148</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" s="5">
+        <v>43.39</v>
+      </c>
+      <c r="I19" t="s">
         <v>149</v>
       </c>
-      <c r="H19" t="s">
+      <c r="J19" s="5">
+        <v>36.729999999999997</v>
+      </c>
+      <c r="K19" t="s">
         <v>150</v>
       </c>
-      <c r="I19" t="s">
+      <c r="L19" s="5">
+        <v>43.82</v>
+      </c>
+      <c r="M19" t="s">
         <v>151</v>
       </c>
-      <c r="J19" t="s">
+      <c r="N19" s="9">
+        <v>40.590000000000003</v>
+      </c>
+      <c r="O19" t="s">
         <v>152</v>
       </c>
-      <c r="K19" t="s">
+      <c r="P19" s="5">
+        <v>41.21</v>
+      </c>
+      <c r="Q19" t="s">
         <v>153</v>
       </c>
+      <c r="R19" s="14">
+        <v>39.44</v>
+      </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2029,26 +3183,47 @@
       <c r="E20" t="s">
         <v>147</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="5">
+        <v>41.5</v>
+      </c>
+      <c r="G20" t="s">
         <v>156</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" s="5">
+        <v>42.03</v>
+      </c>
+      <c r="I20" t="s">
         <v>157</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" s="5">
+        <v>38.74</v>
+      </c>
+      <c r="K20" t="s">
         <v>158</v>
       </c>
-      <c r="I20" t="s">
+      <c r="L20" s="5">
+        <v>43.4</v>
+      </c>
+      <c r="M20" t="s">
         <v>159</v>
       </c>
-      <c r="J20" t="s">
+      <c r="N20" s="9">
+        <v>39.49</v>
+      </c>
+      <c r="O20" t="s">
         <v>160</v>
       </c>
-      <c r="K20" t="s">
+      <c r="P20" s="5">
+        <v>41.3</v>
+      </c>
+      <c r="Q20" t="s">
         <v>161</v>
       </c>
+      <c r="R20" s="12">
+        <v>38.68</v>
+      </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2064,26 +3239,47 @@
       <c r="E21" t="s">
         <v>164</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="5">
+        <v>37.950000000000003</v>
+      </c>
+      <c r="G21" t="s">
         <v>165</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" s="5">
+        <v>39.78</v>
+      </c>
+      <c r="I21" t="s">
         <v>166</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" s="5">
+        <v>35.29</v>
+      </c>
+      <c r="K21" t="s">
         <v>167</v>
       </c>
-      <c r="I21" t="s">
+      <c r="L21" s="5">
+        <v>40.47</v>
+      </c>
+      <c r="M21" t="s">
         <v>168</v>
       </c>
-      <c r="J21" t="s">
+      <c r="N21" s="5">
+        <v>38.090000000000003</v>
+      </c>
+      <c r="O21" t="s">
         <v>169</v>
       </c>
-      <c r="K21" t="s">
+      <c r="P21" s="5">
+        <v>38.82</v>
+      </c>
+      <c r="Q21" t="s">
         <v>170</v>
       </c>
+      <c r="R21" s="12">
+        <v>38</v>
+      </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2099,26 +3295,48 @@
       <c r="E22" t="s">
         <v>12</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" t="s">
         <v>156</v>
       </c>
-      <c r="G22" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="H22" s="5">
+        <v>34.29</v>
+      </c>
+      <c r="I22" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="K22" t="s">
         <v>173</v>
       </c>
-      <c r="I22" t="s">
+      <c r="L22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="M22" t="s">
         <v>174</v>
       </c>
-      <c r="J22" t="s">
-        <v>30</v>
-      </c>
-      <c r="K22" t="s">
-        <v>30</v>
+      <c r="N22" s="9">
+        <f>832.56/30</f>
+        <v>27.751999999999999</v>
+      </c>
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>30</v>
+      </c>
+      <c r="R22" s="12" t="s">
+        <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2134,26 +3352,48 @@
       <c r="E23" t="s">
         <v>30</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G23" t="s">
         <v>177</v>
       </c>
-      <c r="G23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="H23" s="5">
+        <f>32.55*24</f>
+        <v>781.19999999999993</v>
+      </c>
+      <c r="I23" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="K23" t="s">
         <v>173</v>
       </c>
-      <c r="I23" t="s">
+      <c r="L23" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="M23" t="s">
         <v>178</v>
       </c>
-      <c r="J23" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" t="s">
-        <v>30</v>
+      <c r="N23" s="9">
+        <v>650.20000000000005</v>
+      </c>
+      <c r="O23" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>30</v>
+      </c>
+      <c r="R23" s="12" t="s">
+        <v>313</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2169,26 +3409,48 @@
       <c r="E24" t="s">
         <v>181</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="5">
+        <v>649.95799999999997</v>
+      </c>
+      <c r="G24" t="s">
         <v>182</v>
       </c>
-      <c r="G24" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" t="s">
+      <c r="H24" s="5">
+        <f>33.27*24</f>
+        <v>798.48</v>
+      </c>
+      <c r="I24" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="K24" t="s">
         <v>173</v>
       </c>
-      <c r="I24" t="s">
+      <c r="L24" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="M24" t="s">
         <v>183</v>
       </c>
-      <c r="J24" t="s">
-        <v>30</v>
-      </c>
-      <c r="K24" t="s">
-        <v>30</v>
+      <c r="N24" s="9">
+        <v>624.16</v>
+      </c>
+      <c r="O24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>30</v>
+      </c>
+      <c r="R24" s="12" t="s">
+        <v>313</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -2204,26 +3466,49 @@
       <c r="E25" t="s">
         <v>30</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="G25" t="s">
         <v>186</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" s="6">
+        <f t="shared" ref="H25:H26" si="0">52*12</f>
+        <v>624</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K25" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="I25" t="s">
+      <c r="L25" s="6">
+        <f>38.15*12</f>
+        <v>457.79999999999995</v>
+      </c>
+      <c r="M25" t="s">
         <v>188</v>
       </c>
-      <c r="J25" t="s">
+      <c r="N25" s="9">
+        <v>466.82</v>
+      </c>
+      <c r="O25" t="s">
         <v>189</v>
       </c>
-      <c r="K25" t="s">
+      <c r="P25" s="6">
+        <v>570.24</v>
+      </c>
+      <c r="Q25" t="s">
         <v>119</v>
       </c>
+      <c r="R25" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -2239,26 +3524,52 @@
       <c r="E26" t="s">
         <v>30</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="G26" t="s">
         <v>186</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" s="6">
+        <f t="shared" si="0"/>
+        <v>624</v>
+      </c>
+      <c r="I26" t="s">
         <v>192</v>
       </c>
-      <c r="H26" t="s">
+      <c r="J26" s="6">
+        <f>39.1*12</f>
+        <v>469.20000000000005</v>
+      </c>
+      <c r="K26" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I26" t="s">
+      <c r="L26" s="6">
+        <f>41.43*12</f>
+        <v>497.15999999999997</v>
+      </c>
+      <c r="M26" t="s">
         <v>194</v>
       </c>
-      <c r="J26" t="s">
+      <c r="N26" s="9">
+        <f>39.11*12</f>
+        <v>469.32</v>
+      </c>
+      <c r="O26" t="s">
         <v>195</v>
       </c>
-      <c r="K26" t="s">
+      <c r="P26" s="6">
+        <f>44.11*12</f>
+        <v>529.31999999999994</v>
+      </c>
+      <c r="Q26" t="s">
         <v>119</v>
       </c>
+      <c r="R26" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -2274,26 +3585,52 @@
       <c r="E27" t="s">
         <v>198</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="6">
+        <v>434.95</v>
+      </c>
+      <c r="G27" t="s">
         <v>199</v>
       </c>
-      <c r="G27" t="s">
-        <v>200</v>
-      </c>
-      <c r="H27" t="s">
-        <v>201</v>
+      <c r="H27" s="10">
+        <f>32.08*12</f>
+        <v>384.96</v>
       </c>
       <c r="I27" t="s">
         <v>200</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="6">
+        <f>34.69*12</f>
+        <v>416.28</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="L27" s="6">
+        <f>37.25*12</f>
+        <v>447</v>
+      </c>
+      <c r="M27" t="s">
+        <v>200</v>
+      </c>
+      <c r="N27" s="9">
+        <f>34.69*12</f>
+        <v>416.28</v>
+      </c>
+      <c r="O27" t="s">
         <v>202</v>
       </c>
-      <c r="K27" t="s">
+      <c r="P27" s="6">
+        <f>37.35*12</f>
+        <v>448.20000000000005</v>
+      </c>
+      <c r="Q27" t="s">
         <v>119</v>
       </c>
+      <c r="R27" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -2309,26 +3646,49 @@
       <c r="E28" t="s">
         <v>30</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="G28" t="s">
         <v>205</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" s="6">
+        <f>39.13*24</f>
+        <v>939.12000000000012</v>
+      </c>
+      <c r="I28" t="s">
         <v>206</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" s="7">
+        <v>668.62</v>
+      </c>
+      <c r="K28" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="I28" t="s">
+      <c r="L28" s="6">
+        <f>34.02*24</f>
+        <v>816.48</v>
+      </c>
+      <c r="M28" t="s">
         <v>208</v>
       </c>
-      <c r="J28" t="s">
+      <c r="N28" s="9">
+        <v>677.3</v>
+      </c>
+      <c r="O28" t="s">
         <v>209</v>
       </c>
-      <c r="K28" t="s">
+      <c r="P28" s="6">
+        <v>747.12</v>
+      </c>
+      <c r="Q28" t="s">
         <v>119</v>
       </c>
+      <c r="R28" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -2344,26 +3704,48 @@
       <c r="E29" t="s">
         <v>212</v>
       </c>
-      <c r="F29" t="s">
-        <v>30</v>
+      <c r="F29" s="5">
+        <v>169.95</v>
       </c>
       <c r="G29" t="s">
+        <v>30</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I29" t="s">
         <v>213</v>
       </c>
-      <c r="H29" t="s">
-        <v>30</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="J29" s="5">
+        <f>25.94*6</f>
+        <v>155.64000000000001</v>
+      </c>
+      <c r="K29" t="s">
+        <v>30</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M29" t="s">
         <v>214</v>
       </c>
-      <c r="J29" t="s">
+      <c r="N29" s="9">
+        <v>166.25</v>
+      </c>
+      <c r="O29" t="s">
         <v>215</v>
       </c>
-      <c r="K29" t="s">
+      <c r="P29" s="5">
+        <v>189.24</v>
+      </c>
+      <c r="Q29" t="s">
         <v>216</v>
       </c>
+      <c r="R29" s="12">
+        <v>160</v>
+      </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -2379,26 +3761,48 @@
       <c r="E30" t="s">
         <v>219</v>
       </c>
-      <c r="F30" t="s">
-        <v>30</v>
+      <c r="F30" s="5">
+        <v>164.95</v>
       </c>
       <c r="G30" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I30" t="s">
         <v>220</v>
       </c>
-      <c r="H30" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" t="s">
+      <c r="J30" s="5">
+        <f>35.23*4</f>
+        <v>140.91999999999999</v>
+      </c>
+      <c r="K30" t="s">
+        <v>30</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M30" t="s">
         <v>221</v>
       </c>
-      <c r="J30" t="s">
+      <c r="N30" s="9">
+        <v>143.41999999999999</v>
+      </c>
+      <c r="O30" t="s">
         <v>222</v>
       </c>
-      <c r="K30" t="s">
+      <c r="P30" s="5">
+        <v>182.32</v>
+      </c>
+      <c r="Q30" t="s">
         <v>223</v>
       </c>
+      <c r="R30" s="6">
+        <v>155</v>
+      </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -2414,26 +3818,48 @@
       <c r="E31" t="s">
         <v>219</v>
       </c>
-      <c r="F31" t="s">
-        <v>30</v>
+      <c r="F31" s="5">
+        <v>164.95</v>
       </c>
       <c r="G31" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I31" t="s">
         <v>226</v>
       </c>
-      <c r="H31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="J31" s="5">
+        <f>43.68*3</f>
+        <v>131.04</v>
+      </c>
+      <c r="K31" t="s">
+        <v>30</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M31" t="s">
         <v>227</v>
       </c>
-      <c r="J31" t="s">
+      <c r="N31" s="9">
+        <v>129.56</v>
+      </c>
+      <c r="O31" t="s">
         <v>228</v>
       </c>
-      <c r="K31" t="s">
+      <c r="P31" s="5">
+        <v>164.79</v>
+      </c>
+      <c r="Q31" t="s">
         <v>229</v>
       </c>
+      <c r="R31" s="12">
+        <v>140</v>
+      </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -2449,26 +3875,48 @@
       <c r="E32" t="s">
         <v>212</v>
       </c>
-      <c r="F32" t="s">
-        <v>30</v>
+      <c r="F32" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="G32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I32" t="s">
         <v>232</v>
       </c>
-      <c r="H32" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" t="s">
+      <c r="J32" s="5">
+        <f>53.17*2</f>
+        <v>106.34</v>
+      </c>
+      <c r="K32" t="s">
+        <v>30</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M32" t="s">
         <v>233</v>
       </c>
-      <c r="J32" t="s">
+      <c r="N32" s="9">
+        <v>107.58</v>
+      </c>
+      <c r="O32" t="s">
         <v>234</v>
       </c>
-      <c r="K32" t="s">
+      <c r="P32" s="11">
+        <v>131.96</v>
+      </c>
+      <c r="Q32" t="s">
         <v>235</v>
       </c>
+      <c r="R32" s="15">
+        <v>114</v>
+      </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -2484,26 +3932,48 @@
       <c r="E33" t="s">
         <v>238</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="5">
+        <v>159.94999999999999</v>
+      </c>
+      <c r="G33" t="s">
         <v>239</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" s="5">
+        <f>37.08*4</f>
+        <v>148.32</v>
+      </c>
+      <c r="I33" t="s">
         <v>240</v>
       </c>
-      <c r="H33" t="s">
+      <c r="J33" s="5">
+        <v>147.29</v>
+      </c>
+      <c r="K33" t="s">
         <v>241</v>
       </c>
-      <c r="I33" t="s">
+      <c r="L33" s="5">
+        <v>167.27</v>
+      </c>
+      <c r="M33" t="s">
         <v>242</v>
       </c>
-      <c r="J33" t="s">
+      <c r="N33" s="9">
+        <v>142.96</v>
+      </c>
+      <c r="O33" t="s">
         <v>243</v>
       </c>
-      <c r="K33" t="s">
+      <c r="P33" s="5">
+        <v>184.46</v>
+      </c>
+      <c r="Q33" t="s">
         <v>244</v>
       </c>
+      <c r="R33" s="12">
+        <v>144</v>
+      </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -2519,61 +3989,105 @@
       <c r="E34" t="s">
         <v>247</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="5">
+        <v>119.95</v>
+      </c>
+      <c r="G34" t="s">
         <v>248</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" s="5">
+        <f>54.58*2</f>
+        <v>109.16</v>
+      </c>
+      <c r="I34" t="s">
         <v>249</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J34" s="5">
+        <v>109.04</v>
+      </c>
+      <c r="K34" t="s">
         <v>250</v>
       </c>
-      <c r="I34" t="s">
+      <c r="L34" s="5">
+        <v>118.39</v>
+      </c>
+      <c r="M34" t="s">
         <v>251</v>
       </c>
-      <c r="J34" t="s">
+      <c r="N34" s="9">
+        <v>101.32</v>
+      </c>
+      <c r="O34" t="s">
         <v>252</v>
       </c>
-      <c r="K34" t="s">
+      <c r="P34" s="5">
+        <v>137.34</v>
+      </c>
+      <c r="Q34" t="s">
         <v>253</v>
       </c>
+      <c r="R34" s="12">
+        <v>102</v>
+      </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+    <row r="35" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="D35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="9">
+        <v>79.95</v>
+      </c>
+      <c r="G35" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" s="5">
+        <f>19.25*4</f>
+        <v>77</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="H35" t="s">
+      <c r="J35" s="5">
+        <v>77.040000000000006</v>
+      </c>
+      <c r="K35" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="I35" t="s">
+      <c r="L35" s="5">
+        <v>106.02</v>
+      </c>
+      <c r="M35" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="J35" t="s">
+      <c r="N35" s="9">
+        <v>77.040000000000006</v>
+      </c>
+      <c r="O35" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="K35" t="s">
+      <c r="P35" s="5">
+        <v>89.77</v>
+      </c>
+      <c r="Q35" s="2" t="s">
         <v>261</v>
       </c>
+      <c r="R35" s="12">
+        <v>80.88</v>
+      </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -2589,26 +4103,47 @@
       <c r="E36" t="s">
         <v>264</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="5">
+        <v>9.5</v>
+      </c>
+      <c r="G36" t="s">
         <v>265</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" s="5">
+        <v>9.16</v>
+      </c>
+      <c r="I36" t="s">
         <v>266</v>
       </c>
-      <c r="H36" t="s">
+      <c r="J36" s="7">
+        <v>8.58</v>
+      </c>
+      <c r="K36" t="s">
         <v>259</v>
       </c>
-      <c r="I36" t="s">
+      <c r="L36" s="5">
+        <v>9.4</v>
+      </c>
+      <c r="M36" t="s">
         <v>267</v>
       </c>
-      <c r="J36" t="s">
+      <c r="N36" s="9">
+        <v>9.35</v>
+      </c>
+      <c r="O36" t="s">
         <v>268</v>
       </c>
-      <c r="K36" t="s">
+      <c r="P36" s="5">
+        <v>9.35</v>
+      </c>
+      <c r="Q36" t="s">
         <v>269</v>
       </c>
+      <c r="R36" s="12">
+        <v>9.15</v>
+      </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -2624,26 +4159,47 @@
       <c r="E37" t="s">
         <v>30</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="G37" t="s">
         <v>272</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" s="5">
+        <v>11.25</v>
+      </c>
+      <c r="I37" t="s">
         <v>273</v>
       </c>
-      <c r="H37" t="s">
+      <c r="J37" s="5">
+        <v>6.42</v>
+      </c>
+      <c r="K37" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="I37" t="s">
+      <c r="L37" s="5">
+        <v>8.58</v>
+      </c>
+      <c r="M37" t="s">
         <v>274</v>
       </c>
-      <c r="J37" t="s">
+      <c r="N37" s="5">
+        <v>11.4</v>
+      </c>
+      <c r="O37" t="s">
         <v>275</v>
       </c>
-      <c r="K37" t="s">
+      <c r="P37" s="5">
+        <v>5.99</v>
+      </c>
+      <c r="Q37" t="s">
         <v>276</v>
       </c>
+      <c r="R37" s="12">
+        <v>5.75</v>
+      </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -2659,26 +4215,47 @@
       <c r="E38" t="s">
         <v>279</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="5">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="G38" t="s">
         <v>265</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" s="5">
+        <v>9.23</v>
+      </c>
+      <c r="I38" t="s">
         <v>280</v>
       </c>
-      <c r="H38" t="s">
+      <c r="J38" s="5">
+        <v>9.36</v>
+      </c>
+      <c r="K38" t="s">
         <v>259</v>
       </c>
-      <c r="I38" t="s">
+      <c r="L38" s="5">
+        <v>13.59</v>
+      </c>
+      <c r="M38" t="s">
         <v>281</v>
       </c>
-      <c r="J38" t="s">
+      <c r="N38" s="5">
+        <v>12.99</v>
+      </c>
+      <c r="O38" t="s">
         <v>282</v>
       </c>
-      <c r="K38" t="s">
+      <c r="P38" s="5">
+        <v>9.81</v>
+      </c>
+      <c r="Q38" t="s">
         <v>283</v>
       </c>
+      <c r="R38" s="12">
+        <v>14.99</v>
+      </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -2694,26 +4271,47 @@
       <c r="E39" t="s">
         <v>286</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="5">
+        <v>11.5</v>
+      </c>
+      <c r="G39" t="s">
         <v>287</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" s="5">
+        <v>9.58</v>
+      </c>
+      <c r="I39" t="s">
         <v>288</v>
       </c>
-      <c r="H39" t="s">
+      <c r="J39" s="5">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="K39" t="s">
         <v>259</v>
       </c>
-      <c r="I39" t="s">
+      <c r="L39" s="5">
+        <v>9.73</v>
+      </c>
+      <c r="M39" t="s">
         <v>289</v>
       </c>
-      <c r="J39" t="s">
+      <c r="N39" s="5">
+        <v>10.28</v>
+      </c>
+      <c r="O39" t="s">
         <v>290</v>
       </c>
-      <c r="K39" t="s">
+      <c r="P39" s="5">
+        <v>9.15</v>
+      </c>
+      <c r="Q39" t="s">
         <v>291</v>
       </c>
+      <c r="R39" s="12">
+        <v>9.19</v>
+      </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -2729,26 +4327,47 @@
       <c r="E40" t="s">
         <v>12</v>
       </c>
-      <c r="F40" t="s">
-        <v>30</v>
+      <c r="F40" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="G40" t="s">
         <v>30</v>
       </c>
-      <c r="H40" t="s">
-        <v>30</v>
+      <c r="H40" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="I40" t="s">
         <v>30</v>
       </c>
-      <c r="J40" t="s">
-        <v>30</v>
+      <c r="J40" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="K40" t="s">
+        <v>30</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M40" t="s">
+        <v>30</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O40" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q40" t="s">
         <v>294</v>
       </c>
+      <c r="R40" s="12">
+        <v>14.38</v>
+      </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -2764,26 +4383,47 @@
       <c r="E41" t="s">
         <v>12</v>
       </c>
-      <c r="F41" t="s">
-        <v>30</v>
+      <c r="F41" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="G41" t="s">
         <v>30</v>
       </c>
-      <c r="H41" t="s">
-        <v>30</v>
+      <c r="H41" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="I41" t="s">
         <v>30</v>
       </c>
-      <c r="J41" t="s">
-        <v>30</v>
+      <c r="J41" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="K41" t="s">
+        <v>30</v>
+      </c>
+      <c r="L41" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M41" t="s">
+        <v>30</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O41" t="s">
+        <v>30</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q41" t="s">
         <v>297</v>
       </c>
+      <c r="R41" s="12">
+        <v>11.53</v>
+      </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -2799,26 +4439,47 @@
       <c r="E42" t="s">
         <v>12</v>
       </c>
-      <c r="F42" t="s">
-        <v>30</v>
+      <c r="F42" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="G42" t="s">
         <v>30</v>
       </c>
-      <c r="H42" t="s">
-        <v>30</v>
+      <c r="H42" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="I42" t="s">
         <v>30</v>
       </c>
-      <c r="J42" t="s">
-        <v>30</v>
+      <c r="J42" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="K42" t="s">
+        <v>30</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M42" t="s">
+        <v>30</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O42" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q42" t="s">
         <v>300</v>
       </c>
+      <c r="R42" s="12">
+        <v>11.88</v>
+      </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -2834,26 +4495,47 @@
       <c r="E43" t="s">
         <v>12</v>
       </c>
-      <c r="F43" t="s">
-        <v>30</v>
+      <c r="F43" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="G43" t="s">
         <v>30</v>
       </c>
-      <c r="H43" t="s">
-        <v>30</v>
+      <c r="H43" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="I43" t="s">
         <v>30</v>
       </c>
-      <c r="J43" t="s">
-        <v>30</v>
+      <c r="J43" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="K43" t="s">
+        <v>30</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M43" t="s">
+        <v>30</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O43" t="s">
+        <v>30</v>
+      </c>
+      <c r="P43" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q43" t="s">
         <v>303</v>
       </c>
+      <c r="R43" s="12">
+        <v>9.33</v>
+      </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -2869,26 +4551,47 @@
       <c r="E44" t="s">
         <v>30</v>
       </c>
-      <c r="F44" t="s">
-        <v>30</v>
+      <c r="F44" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="G44" t="s">
         <v>30</v>
       </c>
-      <c r="H44" t="s">
-        <v>30</v>
+      <c r="H44" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="I44" t="s">
         <v>30</v>
       </c>
-      <c r="J44" t="s">
-        <v>30</v>
+      <c r="J44" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="K44" t="s">
+        <v>30</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M44" t="s">
+        <v>30</v>
+      </c>
+      <c r="N44" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O44" t="s">
+        <v>30</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q44" t="s">
         <v>306</v>
       </c>
+      <c r="R44" s="12">
+        <v>11.36</v>
+      </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -2904,26 +4607,47 @@
       <c r="E45" t="s">
         <v>12</v>
       </c>
-      <c r="F45" t="s">
-        <v>30</v>
+      <c r="F45" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="G45" t="s">
         <v>30</v>
       </c>
-      <c r="H45" t="s">
-        <v>30</v>
+      <c r="H45" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="I45" t="s">
         <v>30</v>
       </c>
-      <c r="J45" t="s">
-        <v>30</v>
+      <c r="J45" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="K45" t="s">
+        <v>30</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M45" t="s">
+        <v>30</v>
+      </c>
+      <c r="N45" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O45" t="s">
+        <v>30</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q45" t="s">
         <v>309</v>
       </c>
+      <c r="R45" s="12">
+        <v>12.63</v>
+      </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -2939,26 +4663,106 @@
       <c r="E46" t="s">
         <v>12</v>
       </c>
-      <c r="F46" t="s">
-        <v>30</v>
+      <c r="F46" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="G46" t="s">
         <v>30</v>
       </c>
-      <c r="H46" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" t="s">
-        <v>30</v>
+      <c r="H46" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="J46" t="s">
         <v>30</v>
       </c>
       <c r="K46" t="s">
+        <v>30</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="M46" t="s">
+        <v>30</v>
+      </c>
+      <c r="N46" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="O46" t="s">
         <v>312</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="12">
+        <v>15.4</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="J2:J14">
+    <cfRule type="expression" dxfId="12" priority="9">
+      <formula>J2=MIN($G1:$R1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J15:J28">
+    <cfRule type="expression" dxfId="11" priority="11">
+      <formula>J15=MIN($G15:$R15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J29:J34">
+    <cfRule type="expression" dxfId="10" priority="13">
+      <formula>J29=MIN($G30:$R30)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J35">
+    <cfRule type="expression" dxfId="9" priority="15">
+      <formula>J35=MIN($G38:$R38)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I46 J42:J45">
+    <cfRule type="expression" dxfId="8" priority="16">
+      <formula>I42=MIN($F46:$Q46)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J36:J41">
+    <cfRule type="expression" dxfId="7" priority="19">
+      <formula>J36=MIN($G40:$R40)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F46">
+    <cfRule type="expression" dxfId="6" priority="22">
+      <formula>F2=MIN($F1:$Q1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H46">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>H2=MIN($F2:$M2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L46">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>L2=MIN($F2:$M2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:N46">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>N2=MIN($F2:$M2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P46">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>P2=MIN($F2:$M2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R46">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>R2=MIN($F2:$M2)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>